--- a/output/pdf_financials_xlsx/CLV.xlsx
+++ b/output/pdf_financials_xlsx/CLV.xlsx
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>2.885325</v>
+        <v>0.018357</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1.405202</v>
+        <v>-0.000806</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>1.796069</v>
@@ -1164,16 +1164,16 @@
         <v>0.202041</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>0.017757</v>
@@ -1204,10 +1204,10 @@
         <v>-0.702198</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0.146198</v>
+        <v>-3.44594</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.057854</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>-0</v>
@@ -1401,31 +1401,31 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.433484</v>
+        <v>-1.433484</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.703004</v>
+        <v>-0.703004</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1.649871</v>
+        <v>-1.649871</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.528927</v>
+        <v>-3.528927</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>0.202041</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>0.017757</v>
@@ -1548,31 +1548,31 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.433484</v>
+        <v>-1.433484</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.703004</v>
+        <v>-0.703004</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1.649871</v>
+        <v>-1.649871</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.528927</v>
+        <v>-3.528927</v>
       </c>
       <c r="F23" s="3" t="n">
         <v>0.202041</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>0.017757</v>
@@ -1707,16 +1707,16 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>15.9276</v>
+        <v>-15.9276</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>17.5751</v>
+        <v>-17.5751</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>41.246775</v>
+        <v>-41.246775</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>50.413243</v>
+        <v>-50.413243</v>
       </c>
       <c r="F26" s="1" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.07825</v>
+        <v>-17.07825</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2.885325</v>
+        <v>0.018357</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.405202</v>
+        <v>-0.000806</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>1.796069</v>
@@ -1789,16 +1789,16 @@
         <v>0.202041</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>0.017757</v>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>2.885325</v>
+        <v>0.018357</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.405202</v>
+        <v>-0.000806</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>1.796069</v>
@@ -1887,16 +1887,16 @@
         <v>0.202041</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>0.017757</v>
@@ -1998,31 +1998,31 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>50.31810974500273</v>
+        <v>7908.923026638339</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>49.97132084924445</v>
+        <v>-87121.3399503722</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>8.139887721462816</v>
+        <v>191.8601122785372</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0</v>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>1.046058</v>
+        <v>-0.567477</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.134628</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -21488,7 +21488,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
         <v>-1.613535</v>
       </c>
@@ -22692,10 +22696,10 @@
         </is>
       </c>
       <c r="G180" s="5" t="n">
-        <v>1.649871</v>
+        <v>-1.649871</v>
       </c>
       <c r="H180" s="5" t="n">
-        <v>3.528927</v>
+        <v>-3.528927</v>
       </c>
       <c r="I180" t="inlineStr">
         <is>
@@ -22703,16 +22707,16 @@
         </is>
       </c>
       <c r="J180" s="5" t="n">
-        <v>0.533684</v>
+        <v>-0.533684</v>
       </c>
       <c r="K180" s="5" t="n">
-        <v>0.68313</v>
+        <v>-0.68313</v>
       </c>
       <c r="L180" s="5" t="n">
-        <v>0.254513</v>
+        <v>-0.254513</v>
       </c>
       <c r="M180" s="5" t="n">
-        <v>0.253274</v>
+        <v>-0.253274</v>
       </c>
       <c r="N180" t="inlineStr">
         <is>
@@ -27344,10 +27348,10 @@
         </is>
       </c>
       <c r="E236" s="5" t="n">
-        <v>1.433484</v>
+        <v>-1.433484</v>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.703004</v>
+        <v>-0.703004</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CLV.xlsx
+++ b/output/pdf_financials_xlsx/CLV.xlsx
@@ -2131,46 +2131,46 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.001211</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.320531</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009613</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000221</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.838809</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.323102</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.670174</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.365894</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.125794</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.08999</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.346492</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.171131</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.019563</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.670671</v>
       </c>
     </row>
     <row r="35">
@@ -2229,46 +2229,46 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.001211</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.320531</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009613</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000221</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.1045</v>
+        <v>0.943309</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.323102</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.670174</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.365894</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.125794</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.08999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.346492</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.171131</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.019563</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.670671</v>
       </c>
     </row>
     <row r="37">
@@ -2817,46 +2817,46 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.002468</v>
+        <v>0.001257</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.338146</v>
+        <v>0.017615</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.037188</v>
+        <v>0.027575</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.035543</v>
+        <v>0.035322</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.841634</v>
+        <v>0.002825</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.671674</v>
+        <v>0.0015</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.367394</v>
+        <v>0.0015</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.127294</v>
+        <v>0.0015</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.094236</v>
+        <v>0.004246</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.350875</v>
+        <v>0.004383</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.045471</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.021108</v>
+        <v>0.001545</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.672216</v>
+        <v>0.001545</v>
       </c>
     </row>
     <row r="49">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">

--- a/output/pdf_financials_xlsx/CLV.xlsx
+++ b/output/pdf_financials_xlsx/CLV.xlsx
@@ -1204,7 +1204,7 @@
         <v>-0.702198</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-3.44594</v>
+        <v>0.146198</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-7.057854</v>
@@ -2004,7 +2004,7 @@
         <v>-87121.3399503722</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>191.8601122785372</v>
+        <v>8.139887721462816</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>200</v>
@@ -3797,37 +3797,37 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.058</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.027978</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.021999</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.02217</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.02796</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.023722</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.03475</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.036635</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.033</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.043443</v>
       </c>
     </row>
     <row r="68">
@@ -5560,10 +5560,10 @@
         <v>-0.012267</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.005879</v>
       </c>
       <c r="O101" s="3" t="n">
-        <v>0</v>
+        <v>0.122562</v>
       </c>
     </row>
     <row r="102">
@@ -5845,10 +5845,10 @@
         <v>-0.043844</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.004612</v>
+        <v>0.010491</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.080669</v>
+        <v>0.203231</v>
       </c>
     </row>
     <row r="107">
@@ -6274,7 +6274,7 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.9856239999999999</v>
       </c>
       <c r="H114" s="1" t="inlineStr">
         <is>
@@ -6328,10 +6328,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.954377</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.768711</v>
       </c>
       <c r="H115" s="1" t="inlineStr">
         <is>
@@ -16810,7 +16810,11 @@
           <t>Amounts and HST receivable</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -17378,7 +17382,11 @@
           <t>Proceeds from shares issued on private placement,</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -19486,7 +19494,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -19570,7 +19582,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -26908,7 +26924,11 @@
           <t>Income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
